--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -257,7 +257,7 @@
     <t xml:space="preserve">[Optional] Human-readable description of what this weight corrects for.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only — a rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, use cap_weights in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
+    <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only — a rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, put the cap in weight_bounds in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] How to trim weights: cap (fixed multiplier of mean) or percentile (cap at Nth percentile).</t>

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -260,10 +260,10 @@
     <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only — a rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, put the cap in weight_bounds in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] How to trim weights: cap (fixed multiplier of mean) or percentile (cap at Nth percentile).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Trimming threshold. For cap: max ratio (e.g. 5 = 5x mean). For percentile: a proportion strictly between 0 and 1 (e.g. 0.95 for the 95th percentile), NOT 95.</t>
+    <t xml:space="preserve">[Optional] How to trim weights: cap (a maximum weight, on the weight's own scale) or percentile (cap at the Nth percentile).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Trimming threshold. For cap: the maximum weight, e.g. 5. It must be above the mean weight, which is 1 for a weight normalised to the sample, so on a grossed weight use percentile instead. For percentile: a proportion strictly between 0 and 1 (e.g. 0.95 for the 95th percentile), NOT 95.</t>
   </si>
   <si>
     <t xml:space="preserve">wgt_demo</t>

--- a/modules/weighting/docs/templates/Weight_Config.xlsx
+++ b/modules/weighting/docs/templates/Weight_Config.xlsx
@@ -257,7 +257,7 @@
     <t xml:space="preserve">[Optional] Human-readable description of what this weight corrects for.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only — a rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, put the cap in weight_bounds in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
+    <t xml:space="preserve">[Optional] Whether to cap extreme weights AFTER calculation. Y or N. Design and cell weights only. A rim weight is refused, because capping afterwards breaks the margins raking just calibrated. For rim, put the cap in weight_bounds in Advanced_Settings, which caps DURING calibration and keeps the margins.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] How to trim weights: cap (a maximum weight, on the weight's own scale) or percentile (cap at the Nth percentile).</t>
